--- a/assessment_forms/025_ai_maturity_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/025_ai_maturity_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1027,8 +1027,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_minimal/no_access',_'value':_1}</t>
+          <t>1_-_minimal/no_access</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Minimal/No access', 'value': 1}</t>
+          <t>1 - Minimal/No access</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_difficult/manual_access',_'value':_2}</t>
+          <t>2_-_difficult/manual_access</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Difficult/Manual access', 'value': 2}</t>
+          <t>2 - Difficult/Manual access</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_moderate/partial_centralization',_'value':_3}</t>
+          <t>3_-_moderate/partial_centralization</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Moderate/Partial centralization', 'value': 3}</t>
+          <t>3 - Moderate/Partial centralization</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_good/most_data_accessible',_'value':_4}</t>
+          <t>4_-_good/most_data_accessible</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Good/Most data accessible', 'value': 4}</t>
+          <t>4 - Good/Most data accessible</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_optimal/automated_data_pipelines',_'value':_5}</t>
+          <t>5_-_optimal/automated_data_pipelines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Optimal/Automated data pipelines', 'value': 5}</t>
+          <t>5 - Optimal/Automated data pipelines</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_ad-hoc/poor',_'value':_1}</t>
+          <t>1_-_ad-hoc/poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '1 - Ad-hoc/Poor', 'value': 1}</t>
+          <t>1 - Ad-hoc/Poor</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_basic/manual_checks',_'value':_2}</t>
+          <t>2_-_basic/manual_checks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '2 - Basic/Manual checks', 'value': 2}</t>
+          <t>2 - Basic/Manual checks</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_consistent/defined_standards',_'value':_3}</t>
+          <t>3_-_consistent/defined_standards</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '3 - Consistent/Defined standards', 'value': 3}</t>
+          <t>3 - Consistent/Defined standards</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_high_quality/validated',_'value':_4}</t>
+          <t>4_-_high_quality/validated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '4 - High Quality/Validated', 'value': 4}</t>
+          <t>4 - High Quality/Validated</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_exceptional/automated_validation',_'value':_5}</t>
+          <t>5_-_exceptional/automated_validation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '5 - Exceptional/Automated validation', 'value': 5}</t>
+          <t>5 - Exceptional/Automated validation</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_no_mlops_(manual_only)',_'value':_1}</t>
+          <t>1_-_no_mlops_(manual_only)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': '1 - No MLOps (Manual only)', 'value': 1}</t>
+          <t>1 - No MLOps (Manual only)</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_basic_version_control',_'value':_2}</t>
+          <t>2_-_basic_version_control</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '2 - Basic version control', 'value': 2}</t>
+          <t>2 - Basic version control</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_repeatable_deployment_process',_'value':_3}</t>
+          <t>3_-_repeatable_deployment_process</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '3 - Repeatable deployment process', 'value': 3}</t>
+          <t>3 - Repeatable deployment process</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_automated_ci/cd_for_models',_'value':_4}</t>
+          <t>4_-_automated_ci/cd_for_models</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '4 - Automated CI/CD for models', 'value': 4}</t>
+          <t>4 - Automated CI/CD for models</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_advanced/self-healing_systems',_'value':_5}</t>
+          <t>5_-_advanced/self-healing_systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '5 - Advanced/Self-healing systems', 'value': 5}</t>
+          <t>5 - Advanced/Self-healing systems</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'none_(outsourced_only)',_'value':_1}</t>
+          <t>none_(outsourced_only)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'None (Outsourced only)', 'value': 1}</t>
+          <t>None (Outsourced only)</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'small/incubating_team',_'value':_2}</t>
+          <t>small/incubating_team</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Small/Incubating team', 'value': 2}</t>
+          <t>Small/Incubating team</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'growing/core_capabilities',_'value':_3}</t>
+          <t>growing/core_capabilities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Growing/Core capabilities', 'value': 3}</t>
+          <t>Growing/Core capabilities</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'strong/distributed_expertise',_'value':_4}</t>
+          <t>strong/distributed_expertise</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Strong/Distributed expertise', 'value': 4}</t>
+          <t>Strong/Distributed expertise</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'world-class/industry_leading',_'value':_5}</t>
+          <t>world-class/industry_leading</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'World-class/Industry leading', 'value': 5}</t>
+          <t>World-class/Industry leading</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_low/skeptical',_'value':_1}</t>
+          <t>1_-_low/skeptical</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '1 - Low/Skeptical', 'value': 1}</t>
+          <t>1 - Low/Skeptical</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_interested/basic_understanding',_'value':_2}</t>
+          <t>2_-_interested/basic_understanding</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '2 - Interested/Basic understanding', 'value': 2}</t>
+          <t>2 - Interested/Basic understanding</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_supportive/strategic_focus',_'value':_3}</t>
+          <t>3_-_supportive/strategic_focus</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': '3 - Supportive/Strategic focus', 'value': 3}</t>
+          <t>3 - Supportive/Strategic focus</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_highly_literate/actively_driving',_'value':_4}</t>
+          <t>4_-_highly_literate/actively_driving</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '4 - Highly literate/Actively driving', 'value': 4}</t>
+          <t>4 - Highly literate/Actively driving</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_visionary/core_to_identity',_'value':_5}</t>
+          <t>5_-_visionary/core_to_identity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '5 - Visionary/Core to identity', 'value': 5}</t>
+          <t>5 - Visionary/Core to identity</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'no_roadmap_exists',_'value':_'none'}</t>
+          <t>no_roadmap_exists</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'No roadmap exists', 'value': 'none'}</t>
+          <t>No roadmap exists</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'short-term/project-based_only',_'value':_'tactical'}</t>
+          <t>short-term/project-based_only</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Short-term/Project-based only', 'value': 'tactical'}</t>
+          <t>Short-term/Project-based only</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'defined_1-3_year_roadmap',_'value':_'strategic'}</t>
+          <t>defined_1-3_year_roadmap</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Defined 1-3 year roadmap', 'value': 'strategic'}</t>
+          <t>Defined 1-3 year roadmap</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'integrated_multi-year_transformational_plan',_'value':_'transformational'}</t>
+          <t>integrated_multi-year_transformational_plan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Integrated multi-year transformational plan', 'value': 'transformational'}</t>
+          <t>Integrated multi-year transformational plan</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'informally_followed',_'value':_'informal'}</t>
+          <t>informally_followed</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Informally followed', 'value': 'informal'}</t>
+          <t>Informally followed</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'formally_documented_&amp;_training_provided',_'value':_'documented'}</t>
+          <t>formally_documented_&amp;_training_provided</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Formally documented &amp; training provided', 'value': 'documented'}</t>
+          <t>Formally documented &amp; training provided</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'strict_enforcement_&amp;_auditing_in_place',_'value':_'audited'}</t>
+          <t>strict_enforcement_&amp;_auditing_in_place</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Strict enforcement &amp; auditing in place', 'value': 'audited'}</t>
+          <t>Strict enforcement &amp; auditing in place</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'data_quality_/_availability',_'value':_'data'}</t>
+          <t>data_quality_/_availability</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Data Quality / Availability', 'value': 'data'}</t>
+          <t>Data Quality / Availability</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'budget_/_funding',_'value':_'funding'}</t>
+          <t>budget_/_funding</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Budget / Funding', 'value': 'funding'}</t>
+          <t>Budget / Funding</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'talent_/_skill_gap',_'value':_'talent'}</t>
+          <t>talent_/_skill_gap</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Talent / Skill Gap', 'value': 'talent'}</t>
+          <t>Talent / Skill Gap</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'legacy_infrastructure',_'value':_'infra'}</t>
+          <t>legacy_infrastructure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Legacy Infrastructure', 'value': 'infra'}</t>
+          <t>Legacy Infrastructure</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'culture_/_resistance_to_change',_'value':_'culture'}</t>
+          <t>culture_/_resistance_to_change</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Culture / Resistance to Change', 'value': 'culture'}</t>
+          <t>Culture / Resistance to Change</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'regulatory_/_legal_concerns',_'value':_'regulatory'}</t>
+          <t>regulatory_/_legal_concerns</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Regulatory / Legal Concerns', 'value': 'regulatory'}</t>
+          <t>Regulatory / Legal Concerns</t>
         </is>
       </c>
     </row>
